--- a/themes/limits.xlsx
+++ b/themes/limits.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -470,159 +470,59 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>60</v>
+        <v>117</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">        • суточный — за последние 24 часа</t>
+          <t xml:space="preserve">          1. Действует период охлаждения – зависит от суммы: </t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">        • суточный — за последние 24 часа.</t>
+          <t xml:space="preserve">          1. Действует период охлаждения — зависит от суммы: </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>добавлена точка — для единообразия со вторым пунктом списка (стр. 61), где точка есть</t>
+          <t>эн-дефис (–) заменён на тире (—)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>87</v>
+        <v>123</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Адреса и режим работы офисов банка вы найдете на нашем [сайте]({{$temp.officeLink}})</t>
+          <t xml:space="preserve">          2. Карта не активирована. В течение дня, после получения карты у курьера, вам поступит смс-сообщение об активации карты и установке PIN-кода.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Адреса и режим работы офисов банка вы найдете на нашем [сайте]({{$temp.officeLink}}).</t>
+          <t xml:space="preserve">          2. Карта не активирована. В течение дня, после получения карты у курьера, вам поступит SMS-сообщение об активации карты и установке PIN-кода.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
+          <t>«смс» приведено к «SMS» — для единообразия с остальными случаями в базе (используется латиницей)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Disagree: По вопросу уменьшения кредитного лимита переключаю вас на оператора  </t>
+          <t xml:space="preserve">          Если период охлаждения закончился и после выдачи карты курьером прошло более 1 календарного дня нажмите на кнопку «Лимит не начислен».</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Disagree: По вопросу уменьшения кредитного лимита переключаю вас на оператора.  </t>
+          <t xml:space="preserve">          Если период охлаждения закончился и после выдачи карты курьером прошло более 1 календарного дня, нажмите на кнопку «Лимит не начислен».</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>101</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    isNotAuthorized: Посмотреть лимит по кредитной карте можно в приложении «Уралсиб Онлайн» в разделе «Кредитная карта» и на главном экране и в веб-версии на [сайте](https://online.uralsib.ru/)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    isNotAuthorized: Посмотреть лимит по кредитной карте можно в приложении «Уралсиб Онлайн» в разделе «Кредитная карта» и на главном экране и в веб-версии на [сайте](https://online.uralsib.ru/).</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>103</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    web: Посмотреть лимит по кредитной карте можно на главном экране и в веб-версии на [сайте](https://online.uralsib.ru/)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    web: Посмотреть лимит по кредитной карте можно на главном экране и в веб-версии на [сайте](https://online.uralsib.ru/).</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>117</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          1. Действует период охлаждения – зависит от суммы: </t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          1. Действует период охлаждения — зависит от суммы: </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>эн-дефис (–) заменён на тире (—)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>123</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          2. Карта не активирована. В течение дня, после получения карты у курьера, вам поступит смс-сообщение об активации карты и установке PIN-кода.</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          2. Карта не активирована. В течение дня, после получения карты у курьера, вам поступит SMS-сообщение об активации карты и установке PIN-кода.</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>«смс» приведено к «SMS» — для единообразия с остальными случаями в базе (используется латиницей)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>125</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          Если период охлаждения закончился и после выдачи карты курьером прошло более 1 календарного дня нажмите на кнопку «Лимит не начислен».</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          Если период охлаждения закончился и после выдачи карты курьером прошло более 1 календарного дня, нажмите на кнопку «Лимит не начислен».</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
         <is>
           <t>добавлена запятая после длинного придаточного условия</t>
         </is>
